--- a/exemples_risk_intelligence/ECOBANK_Audit_Report_2026-09-30.xlsx
+++ b/exemples_risk_intelligence/ECOBANK_Audit_Report_2026-09-30.xlsx
@@ -93,7 +93,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,6 +151,16 @@
         <fgColor rgb="FFEAF2FF"/>
         <bgColor indexed="64"/>
       </patternFill>
+    </fill>
+    <fill>
+      <gradientFill degree="90">
+        <stop position="0">
+          <color rgb="FFFFFFFF"/>
+        </stop>
+        <stop position="1">
+          <color rgb="FFF2F7FF"/>
+        </stop>
+      </gradientFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -215,10 +225,10 @@
         <color rgb="FFDBE6F7"/>
       </right>
       <top style="thin">
-        <color rgb="FFDBE6F7"/>
+        <color rgb="FFFFFFFF"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -230,10 +240,10 @@
         <color rgb="FFDBE6F7"/>
       </right>
       <top style="thin">
-        <color rgb="FFDBE6F7"/>
+        <color rgb="FFFFFFFF"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFDBE6F7"/>
+      <bottom style="medium">
+        <color rgb="FFBCCBE3"/>
       </bottom>
       <diagonal/>
     </border>
@@ -351,25 +361,25 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -378,10 +388,10 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -402,13 +412,101 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Visuel 3D ECOBANK" descr="Skyline de données en verre bleu et anneau or (rendu Blender)"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rIdI1"/>
+        <a:srcRect l="29545" r="29545"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Visuel 3D ECOBANK" descr="Skyline de données en verre bleu et anneau or (rendu Blender)"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rIdI1"/>
+        <a:srcRect t="20226" b="20226"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF001B4D"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -521,6 +619,25 @@
             </rPr>
             <t xml:space="preserve">Traçabilité, contrôles automatiques et provenance</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+30 SEPTEMBER 2026   ·   PORTFOLIO MONITORING</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFBFD3FF"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">
+Portefeuille Ecobank Sénégal · 700 clients · 2 500 lignes ACTE 7</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="3"/>
@@ -627,9 +744,7 @@
       </c>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -650,6 +765,8 @@
           </r>
         </is>
       </c>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
@@ -704,7 +821,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">JEV · PD 12M  </t>
+            <t xml:space="preserve">OUTLOOK · PD 12M  </t>
           </r>
           <r>
             <rPr>
@@ -736,7 +853,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">TYPESAFE  </t>
+            <t xml:space="preserve">SÉMANTIQUE  </t>
           </r>
           <r>
             <rPr>
@@ -745,7 +862,7 @@
               <color rgb="FF001B4D"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">24 retours · 8 en revue</t>
+            <t xml:space="preserve">30 lus · 16 en revue</t>
           </r>
         </is>
       </c>
@@ -854,7 +971,7 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_01.xlsx</t>
+          <t xml:space="preserve">N_01.xlsx</t>
         </is>
       </c>
       <c r="C14" s="16" t="inlineStr">
@@ -876,7 +993,7 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_02.xlsx</t>
+          <t xml:space="preserve">N_02.xlsx</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
@@ -898,7 +1015,7 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_03.xlsx</t>
+          <t xml:space="preserve">N_03.xlsx</t>
         </is>
       </c>
       <c r="C16" s="16" t="inlineStr">
@@ -920,7 +1037,7 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_04.xlsx</t>
+          <t xml:space="preserve">N_04.xlsx</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
@@ -942,7 +1059,7 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_05.xlsx</t>
+          <t xml:space="preserve">N_05.xlsx</t>
         </is>
       </c>
       <c r="C18" s="16" t="inlineStr">
@@ -964,7 +1081,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_06.xlsx</t>
+          <t xml:space="preserve">N_06.xlsx</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -986,7 +1103,7 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_07.xlsx</t>
+          <t xml:space="preserve">N_07.xlsx</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
@@ -1008,7 +1125,7 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_08.xlsx</t>
+          <t xml:space="preserve">N_08.xlsx</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -1030,7 +1147,7 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">M_09.xlsx</t>
+          <t xml:space="preserve">N_09.xlsx</t>
         </is>
       </c>
       <c r="C22" s="16" t="inlineStr">
@@ -1242,7 +1359,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valeurs non numériques (NaN / Infini)</t>
+          <t xml:space="preserve">Valeurs non numériques (non-nombres, infinis)</t>
         </is>
       </c>
       <c r="B32" s="16" t="inlineStr">
@@ -1286,7 +1403,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV : PD avec provenance pour chaque client de la watchlist</t>
+          <t xml:space="preserve">RISK OUTLOOK : PD avec provenance pour chaque client de la watchlist</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
@@ -1469,7 +1586,7 @@
     <row r="45" ht="32" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe</t>
+          <t xml:space="preserve">Analyse sémantique</t>
         </is>
       </c>
       <c r="B45" s="21" t="inlineStr">
@@ -1483,7 +1600,7 @@
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV</t>
+          <t xml:space="preserve">RISK OUTLOOK</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
@@ -1513,7 +1630,7 @@
               <color rgb="FF001B4D"/>
               <sz val="11"/>
             </rPr>
-            <t xml:space="preserve">COUVERTURE JEV &amp; TYPESAFE</t>
+            <t xml:space="preserve">COUVERTURE RISK OUTLOOK &amp; ANALYSE SÉMANTIQUE</t>
           </r>
           <r>
             <rPr>
@@ -1565,7 +1682,7 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · MARKOV / HYBRID</t>
+          <t xml:space="preserve">RISK OUTLOOK · MARKOV / HYBRID</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
@@ -1587,7 +1704,7 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · EMPIRICAL</t>
+          <t xml:space="preserve">RISK OUTLOOK · EMPIRICAL</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
@@ -1609,7 +1726,7 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · STRESS / SIMULATED</t>
+          <t xml:space="preserve">RISK OUTLOOK · STRESS / SIMULATED</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
@@ -1631,7 +1748,7 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · HYBRID (Markov + EWS + expert)</t>
+          <t xml:space="preserve">RISK OUTLOOK · HYBRID (Markov + EWS + expert)</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
@@ -1641,7 +1758,7 @@
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">signaux TypeSafe et APEX en multiplicateurs EXPERT affichés</t>
+          <t xml:space="preserve">signaux Analyse sémantique et APEX en multiplicateurs EXPERT affichés</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1770,7 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">JEV · recalcul par le code</t>
+          <t xml:space="preserve">RISK OUTLOOK · recalcul par le code</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
@@ -1670,127 +1787,369 @@
     <row r="55" ht="19" customHeight="1">
       <c r="A55" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motif, crédibilité, incohérence, statut</t>
+          <t xml:space="preserve">Analyses avancées</t>
         </is>
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe · Choice / Score / Noul</t>
+          <t xml:space="preserve">RISK OUTLOOK · MARKOV / SIMULATED / EMPIRICAL / STRESS</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">✔ 24 dossiers</t>
+          <t xml:space="preserve">✔ actif</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">commentaires gestionnaires (feuille _TYPESAFE)</t>
+          <t xml:space="preserve">structure par terme, temps avant défaut, guérison, IC bootstrap, backtest, stress inverse, sensibilité</t>
         </is>
       </c>
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nature de l'entité, intra-groupe, segment</t>
+          <t xml:space="preserve">Motif, crédibilité, incohérence, statut</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe · Choice / Noul</t>
+          <t xml:space="preserve">Analyse sémantique · Choice / Score / Noul</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">✔ actif</t>
+          <t xml:space="preserve">✔ 30 dossiers</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">noms de clients</t>
+          <t xml:space="preserve">commentaires gestionnaires (feuille _SEMANTIQUE)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Urgence et orientation (re-classement, routage)</t>
+          <t xml:space="preserve">Nature de l'entité, intra-groupe, segment</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe · Score / Choice</t>
+          <t xml:space="preserve">Analyse sémantique · Choice / Noul</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">en attente</t>
+          <t xml:space="preserve">✔ actif</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">capacités avancées</t>
+          <t xml:space="preserve">noms de clients</t>
         </is>
       </c>
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auto-cohérence et cohérence du plan</t>
+          <t xml:space="preserve">Urgence et orientation (re-classement, routage)</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TypeSafe · Noul + Choice croisés</t>
+          <t xml:space="preserve">Analyse sémantique · Score / Choice</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">en attente</t>
+          <t xml:space="preserve">✔ 27 dossiers</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">divergence → revue analyste</t>
+          <t xml:space="preserve">capacités avancées</t>
         </is>
       </c>
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" s="17" t="inlineStr">
         <is>
+          <t xml:space="preserve">Auto-cohérence et cohérence du plan</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Noul + Choice croisés</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">divergence → revue analyste</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dates par composants (jour, mois, relatif)</t>
+        </is>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Choice ; assemblage en code</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">limite connue du modèle : dates comparées en code</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Données personnelles sensibles</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Noul</t>
+        </is>
+      </c>
+      <c r="C61" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">commentaire à anonymiser avant diffusion</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19" customHeight="1">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Famille de motif et repli selon la confiance</t>
+        </is>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Choice hiérarchique</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">motif détaillé incertain → famille retenue si confiance ≥ 0,9</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="19" customHeight="1">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Action recommandée (catalogue du code)</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Choice</t>
+        </is>
+      </c>
+      <c r="C63" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 actions types</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19" customHeight="1">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contrôle d'ordre des options</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Choice inversé</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">divergence → revue analyste</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="19" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stabilité (rééchantillonnage)</t>
+        </is>
+      </c>
+      <c r="B65" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · 3 tirages avec sel</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">instabilité → revue analyste</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stress narratif (8 scénarios macro)</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Noul ; agrégats et PD en code</t>
+        </is>
+      </c>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ 8 scénario(s) avec exposition</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exposition jugée, montants calculés</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="19" customHeight="1">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phrase de lecture et ordre des constats</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Score + Choice (portefeuille)</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ actif</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">constats calculés par le code</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="19" customHeight="1">
+      <c r="A68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bénéficiaires potentiellement liés</t>
+        </is>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Analyse sémantique · Score + Noul (portefeuille)</t>
+        </is>
+      </c>
+      <c r="C68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ 5 paire(s)</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">paires repérées par le code</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Version exacte du modèle et jetons</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Réponse de l'API</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">✔ conservés</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">piste d'audit (_SEMANTIQUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Montants, ratios, classes BCEAO / IFRS 9 / ACTE 7</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">Code APEX uniquement</t>
         </is>
       </c>
-      <c r="C59" s="17" t="inlineStr">
+      <c r="C70" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">✔ code</t>
         </is>
       </c>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jamais confiés à TypeSafe ni à JEV</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Généré le 03/10/2026 13:32:51 · RI 1.0 · APEX Credit Risk OS · source : M_09.xlsx</t>
-        </is>
-      </c>
-      <c r="B61" s="24"/>
-      <c r="C61" s="24"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="24"/>
-      <c r="F61" s="24"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jamais confiés à Analyse sémantique ni à RISK OUTLOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Généré le 03/10/2026 15:12:16 · RI 1.0 · APEX Credit Risk OS · source : N_09.xlsx</t>
+        </is>
+      </c>
+      <c r="B72" s="24"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="24"/>
+      <c r="G72" s="24"/>
+      <c r="H72" s="24"/>
+      <c r="I72" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -1802,8 +2161,8 @@
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="G6:I6"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:I8"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C10:E10"/>
     <mergeCell ref="F10:G10"/>
@@ -1820,10 +2179,10 @@
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A72:I72"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="F8" location="'DETAIL'!A1" display="DETAIL"/>
+    <hyperlink ref="D8" location="'DETAIL'!A1" display="DETAIL"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.45" bottom="0.5" header="0.2" footer="0.25"/>
@@ -1832,6 +2191,7 @@
     <oddHeader>&amp;L&amp;8&amp;K003DA5ECOBANK SÉNÉGAL · CREDIT RISK INTELLIGENCE&amp;R&amp;8&amp;K64748BArrêté 30/09/2026</oddHeader>
     <oddFooter>&amp;L&amp;8&amp;K64748BAUDIT · INTERNAL USE ONLY&amp;R&amp;8&amp;K64748BPage &amp;P / &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1976,6 +2336,25 @@
             </rPr>
             <t xml:space="preserve">Données propres et réutilisables · une ligne par client · source canonique</t>
           </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <b/>
+              <color rgb="FFC8A951"/>
+              <sz val="9"/>
+            </rPr>
+            <t xml:space="preserve">
+30 SEPTEMBER 2026   ·   PORTFOLIO MONITORING</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Segoe UI"/>
+              <color rgb="FFBFD3FF"/>
+              <sz val="7.5"/>
+            </rPr>
+            <t xml:space="preserve">
+Portefeuille Ecobank Sénégal · 700 clients · 2 500 lignes ACTE 7</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="3"/>
@@ -2153,9 +2532,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2176,6 +2553,8 @@
           </r>
         </is>
       </c>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
       <c r="L8" s="10"/>
       <c r="M8" s="10"/>
       <c r="N8" s="10"/>
@@ -2239,7 +2618,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">JEV · PD 12M  </t>
+            <t xml:space="preserve">OUTLOOK · PD 12M  </t>
           </r>
           <r>
             <rPr>
@@ -2273,7 +2652,7 @@
               <color rgb="FF64748B"/>
               <sz val="7"/>
             </rPr>
-            <t xml:space="preserve">TYPESAFE  </t>
+            <t xml:space="preserve">SÉMANTIQUE  </t>
           </r>
           <r>
             <rPr>
@@ -2282,7 +2661,7 @@
               <color rgb="FF001B4D"/>
               <sz val="8.5"/>
             </rPr>
-            <t xml:space="preserve">24 retours · 8 en revue</t>
+            <t xml:space="preserve">30 lus · 16 en revue</t>
           </r>
         </is>
       </c>
@@ -2436,7 +2815,7 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0378</t>
+          <t xml:space="preserve">BAOBAB NEGOCE SA</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -2510,7 +2889,7 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0388</t>
+          <t xml:space="preserve">KORA TRANSPORTS ET FILS</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -2584,7 +2963,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0353</t>
+          <t xml:space="preserve">SAHEL CIMENTS INDUSTRIE SA</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -2666,7 +3045,7 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0483</t>
+          <t xml:space="preserve">TERANGA BATIMENT TRAVAUX PUBLICS</t>
         </is>
       </c>
       <c r="C16" s="27" t="inlineStr">
@@ -2740,7 +3119,7 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0370</t>
+          <t xml:space="preserve">KORA LOGISTIQUE ET TRANSIT</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -2814,7 +3193,7 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0355</t>
+          <t xml:space="preserve">BAOBAB NEGOCE DISTRIBUTION SARL</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
@@ -2978,7 +3357,7 @@
       </c>
       <c r="B20" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0461</t>
+          <t xml:space="preserve">SAHEL PECHE ARMEMENT</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
@@ -3126,7 +3505,7 @@
       </c>
       <c r="B22" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0561</t>
+          <t xml:space="preserve">NIAYES HORTICULTURE EXPORT</t>
         </is>
       </c>
       <c r="C22" s="27" t="inlineStr">
@@ -3208,7 +3587,7 @@
       </c>
       <c r="B23" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0454</t>
+          <t xml:space="preserve">TERANGA IMMOBILIER PROMOTION</t>
         </is>
       </c>
       <c r="C23" s="27" t="inlineStr">
@@ -3282,7 +3661,7 @@
       </c>
       <c r="B24" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">SOCIETE 0364</t>
+          <t xml:space="preserve">COOPERATIVE AGRICOLE DES NIAYES</t>
         </is>
       </c>
       <c r="C24" s="27" t="inlineStr">
@@ -3508,7 +3887,7 @@
       </c>
       <c r="T26" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promesse de règlement</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4807,7 @@
       </c>
       <c r="T38" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promesse de règlement</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -4896,7 +5275,7 @@
       </c>
       <c r="T44" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promesse de règlement</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5743,7 @@
       </c>
       <c r="T50" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">En cours</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -6818,7 +7197,7 @@
       </c>
       <c r="T69" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7657,7 @@
       </c>
       <c r="T75" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revue analyste</t>
+          <t xml:space="preserve">Promesse de règlement</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7895,7 @@
       </c>
       <c r="T78" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">En cours</t>
         </is>
       </c>
     </row>
@@ -7828,7 +8207,7 @@
       </c>
       <c r="T82" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revue analyste</t>
+          <t xml:space="preserve">En cours</t>
         </is>
       </c>
     </row>
@@ -8822,7 +9201,7 @@
       </c>
       <c r="T95" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Promesse de règlement</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -9816,7 +10195,7 @@
       </c>
       <c r="T108" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -14456,7 +14835,7 @@
       </c>
       <c r="T168" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revue analyste</t>
+          <t xml:space="preserve">Restructuration</t>
         </is>
       </c>
     </row>
@@ -15762,7 +16141,7 @@
       </c>
       <c r="T185" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -21750,7 +22129,7 @@
       </c>
       <c r="T263" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">À faire</t>
+          <t xml:space="preserve">Revue analyste</t>
         </is>
       </c>
     </row>
@@ -56587,8 +56966,8 @@
     <mergeCell ref="N4:T4"/>
     <mergeCell ref="N5:T5"/>
     <mergeCell ref="N6:T6"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="I8:T8"/>
     <mergeCell ref="A10:E10"/>
     <mergeCell ref="F10:J10"/>
     <mergeCell ref="K10:O10"/>
@@ -56604,5 +56983,6 @@
     <oddHeader>&amp;L&amp;8&amp;K003DA5ECOBANK SÉNÉGAL · CREDIT RISK INTELLIGENCE&amp;R&amp;8&amp;K64748BArrêté 30/09/2026</oddHeader>
     <oddFooter>&amp;L&amp;8&amp;K64748BDETAIL · INTERNAL USE ONLY&amp;R&amp;8&amp;K64748BPage &amp;P / &amp;N</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>